--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,69 +556,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,174 +871,174 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,199 +1126,199 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,120 +1326,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,124 +671,124 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,116 +797,116 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,425 +916,180 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>The Cadmus Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,50 +1046,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,15 +1046,85 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SR SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,157 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,105 +538,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,50 +941,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,50 +906,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,77 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,295 +556,120 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -635,41 +635,6 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Databricks Architect &amp; Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Kollasoft Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=961f7719b1e41e9a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -635,6 +635,41 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Desarrollador/a Python</t>
+          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PCD Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -635,41 +635,6 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>

--- a/results/job_matches_2026-03-01.xlsx
+++ b/results/job_matches_2026-03-01.xlsx
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Supplied Talent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae7f307250b6639</t>
         </is>
       </c>
     </row>
